--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487594_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487594_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.0594</v>
+        <v>6.0978</v>
       </c>
       <c r="E2" t="n">
-        <v>3.424</v>
+        <v>2.9446</v>
       </c>
       <c r="F2" t="n">
-        <v>2.6354</v>
+        <v>3.1532</v>
       </c>
       <c r="G2" t="n">
         <v>3.6897</v>
@@ -610,13 +610,13 @@
         <v>1.7463</v>
       </c>
       <c r="S2" t="n">
-        <v>0.5291</v>
+        <v>0.5675</v>
       </c>
       <c r="T2" t="n">
-        <v>0.4508</v>
+        <v>-0.0286</v>
       </c>
       <c r="U2" t="n">
-        <v>0.07829999999999999</v>
+        <v>0.5961</v>
       </c>
       <c r="V2" t="n">
         <v>2.0346</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.5011</v>
+        <v>3.774</v>
       </c>
       <c r="E3" t="n">
-        <v>3.3412</v>
+        <v>3.7231</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1598</v>
+        <v>0.0508</v>
       </c>
       <c r="G3" t="n">
         <v>2.1351</v>
@@ -688,13 +688,13 @@
         <v>1.5523</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.1579</v>
+        <v>0.115</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.5933</v>
+        <v>-0.2114</v>
       </c>
       <c r="U3" t="n">
-        <v>0.4354</v>
+        <v>0.3264</v>
       </c>
       <c r="V3" t="n">
         <v>0.9418</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>H. PEREZ SANCHEZ</t>
+          <t>R. LARDIES GUILLEN</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.4297</v>
+        <v>2.3874</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.4698</v>
+        <v>0.7030999999999999</v>
       </c>
       <c r="F4" t="n">
-        <v>2.8995</v>
+        <v>1.6842</v>
       </c>
       <c r="G4" t="n">
-        <v>0.4269</v>
+        <v>1.4626</v>
       </c>
       <c r="H4" t="n">
-        <v>1.1526</v>
+        <v>0.1524</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.7257</v>
+        <v>1.3102</v>
       </c>
       <c r="J4" t="n">
-        <v>0.2057</v>
+        <v>0.7625999999999999</v>
       </c>
       <c r="K4" t="n">
-        <v>0.7868000000000001</v>
+        <v>-0.5643</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.5810999999999999</v>
+        <v>1.3269</v>
       </c>
       <c r="M4" t="n">
-        <v>0.2212</v>
+        <v>0.7</v>
       </c>
       <c r="N4" t="n">
-        <v>0.3658</v>
+        <v>0.7168</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.1446</v>
+        <v>-0.0167</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.194</v>
+        <v>1.3582</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.9403</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.7463</v>
+        <v>1.3582</v>
       </c>
       <c r="S4" t="n">
-        <v>0.6909</v>
+        <v>-0.1514</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.2412</v>
+        <v>-0.0595</v>
       </c>
       <c r="U4" t="n">
-        <v>0.9321</v>
+        <v>-0.092</v>
       </c>
       <c r="V4" t="n">
-        <v>1.506</v>
+        <v>-0.2821</v>
       </c>
       <c r="W4" t="n">
-        <v>1.506</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-0.2821</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>R. LARDIES GUILLEN</t>
+          <t>G. DIAZ MONTERO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.6418</v>
+        <v>2.165</v>
       </c>
       <c r="E5" t="n">
-        <v>0.121</v>
+        <v>0.661</v>
       </c>
       <c r="F5" t="n">
-        <v>1.5207</v>
+        <v>1.5039</v>
       </c>
       <c r="G5" t="n">
-        <v>1.4626</v>
+        <v>3.1829</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1524</v>
+        <v>2.9165</v>
       </c>
       <c r="I5" t="n">
-        <v>1.3102</v>
+        <v>0.2664</v>
       </c>
       <c r="J5" t="n">
-        <v>0.7625999999999999</v>
+        <v>3.7852</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.5643</v>
+        <v>3.2296</v>
       </c>
       <c r="L5" t="n">
-        <v>1.3269</v>
+        <v>0.5556</v>
       </c>
       <c r="M5" t="n">
-        <v>0.7</v>
+        <v>-0.6022999999999999</v>
       </c>
       <c r="N5" t="n">
-        <v>0.7168</v>
+        <v>-0.3131</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.0167</v>
+        <v>-0.2892</v>
       </c>
       <c r="P5" t="n">
-        <v>1.3582</v>
+        <v>-1.1642</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-2.9105</v>
       </c>
       <c r="R5" t="n">
-        <v>1.3582</v>
+        <v>1.7463</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.897</v>
+        <v>0.4761</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.6415999999999999</v>
+        <v>-0.4958</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.2555</v>
+        <v>0.9719</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.2821</v>
+        <v>-0.3299</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>0.2821</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.2821</v>
+        <v>-0.6119</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>J. ATIENZA PEREA</t>
+          <t>N. MAIGA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.5208</v>
+        <v>1.9863</v>
       </c>
       <c r="E6" t="n">
-        <v>2.1511</v>
+        <v>0.3868</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.6303</v>
+        <v>1.5996</v>
       </c>
       <c r="G6" t="n">
-        <v>1.7971</v>
+        <v>1.4357</v>
       </c>
       <c r="H6" t="n">
-        <v>1.5835</v>
+        <v>1.4591</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2136</v>
+        <v>-0.0234</v>
       </c>
       <c r="J6" t="n">
-        <v>2.0424</v>
+        <v>1.2926</v>
       </c>
       <c r="K6" t="n">
-        <v>0.7333</v>
+        <v>1.1658</v>
       </c>
       <c r="L6" t="n">
-        <v>1.3092</v>
+        <v>0.1268</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.2454</v>
+        <v>0.1431</v>
       </c>
       <c r="N6" t="n">
-        <v>0.8502</v>
+        <v>0.2933</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.0956</v>
+        <v>-0.1502</v>
       </c>
       <c r="P6" t="n">
-        <v>1.7463</v>
+        <v>0.5821</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-0.9702</v>
       </c>
       <c r="R6" t="n">
-        <v>1.7463</v>
+        <v>1.5523</v>
       </c>
       <c r="S6" t="n">
-        <v>0.9338</v>
+        <v>0.09950000000000001</v>
       </c>
       <c r="T6" t="n">
-        <v>0.4385</v>
+        <v>-0.5476</v>
       </c>
       <c r="U6" t="n">
-        <v>0.4953</v>
+        <v>0.6472</v>
       </c>
       <c r="V6" t="n">
-        <v>-2.9564</v>
+        <v>-0.131</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.3299</v>
+        <v>0.6119</v>
       </c>
       <c r="X6" t="n">
-        <v>-2.6265</v>
+        <v>-0.743</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>G. DIAZ MONTERO</t>
+          <t>H. PEREZ SANCHEZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.3436</v>
+        <v>1.978</v>
       </c>
       <c r="E7" t="n">
-        <v>0.1395</v>
+        <v>-0.649</v>
       </c>
       <c r="F7" t="n">
-        <v>1.2041</v>
+        <v>2.627</v>
       </c>
       <c r="G7" t="n">
-        <v>3.1829</v>
+        <v>0.4269</v>
       </c>
       <c r="H7" t="n">
-        <v>2.9165</v>
+        <v>1.1526</v>
       </c>
       <c r="I7" t="n">
-        <v>0.2664</v>
+        <v>-0.7257</v>
       </c>
       <c r="J7" t="n">
-        <v>3.7852</v>
+        <v>0.2057</v>
       </c>
       <c r="K7" t="n">
-        <v>3.2296</v>
+        <v>0.7868000000000001</v>
       </c>
       <c r="L7" t="n">
-        <v>0.5556</v>
+        <v>-0.5810999999999999</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.6022999999999999</v>
+        <v>0.2212</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.3131</v>
+        <v>0.3658</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.2892</v>
+        <v>-0.1446</v>
       </c>
       <c r="P7" t="n">
-        <v>-1.1642</v>
+        <v>-0.194</v>
       </c>
       <c r="Q7" t="n">
-        <v>-2.9105</v>
+        <v>-1.9403</v>
       </c>
       <c r="R7" t="n">
         <v>1.7463</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.3452</v>
+        <v>0.2392</v>
       </c>
       <c r="T7" t="n">
-        <v>-1.0173</v>
+        <v>-0.4203</v>
       </c>
       <c r="U7" t="n">
-        <v>0.6721</v>
+        <v>0.6595</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.3299</v>
+        <v>1.506</v>
       </c>
       <c r="W7" t="n">
-        <v>0.2821</v>
+        <v>1.506</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.6119</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>N. MAIGA</t>
+          <t>A. SIMON DEL CORRAL</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>1.3408</v>
+        <v>1.223</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.09520000000000001</v>
+        <v>0.2416</v>
       </c>
       <c r="F8" t="n">
-        <v>1.436</v>
+        <v>0.9814000000000001</v>
       </c>
       <c r="G8" t="n">
-        <v>1.4357</v>
+        <v>-0.1611</v>
       </c>
       <c r="H8" t="n">
-        <v>1.4591</v>
+        <v>-0.0626</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.0234</v>
+        <v>-0.0984</v>
       </c>
       <c r="J8" t="n">
-        <v>1.2926</v>
+        <v>0.123</v>
       </c>
       <c r="K8" t="n">
-        <v>1.1658</v>
+        <v>0.0824</v>
       </c>
       <c r="L8" t="n">
-        <v>0.1268</v>
+        <v>0.0406</v>
       </c>
       <c r="M8" t="n">
-        <v>0.1431</v>
+        <v>-0.284</v>
       </c>
       <c r="N8" t="n">
-        <v>0.2933</v>
+        <v>-0.145</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.1502</v>
+        <v>-0.139</v>
       </c>
       <c r="P8" t="n">
-        <v>0.5821</v>
+        <v>0.3881</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.9702</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.5523</v>
+        <v>0.3881</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.546</v>
+        <v>0.5151</v>
       </c>
       <c r="T8" t="n">
-        <v>-1.0296</v>
+        <v>0.1186</v>
       </c>
       <c r="U8" t="n">
-        <v>0.4836</v>
+        <v>0.3965</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.131</v>
+        <v>0.4809</v>
       </c>
       <c r="W8" t="n">
-        <v>0.6119</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.743</v>
+        <v>0.4809</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A. SIMON DEL CORRAL</t>
+          <t>J. ATIENZA PEREA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>1.271</v>
+        <v>1.1357</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.1193</v>
+        <v>2.093</v>
       </c>
       <c r="F9" t="n">
-        <v>1.3902</v>
+        <v>-0.9574</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.1611</v>
+        <v>1.7971</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.0626</v>
+        <v>1.5835</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.0984</v>
+        <v>0.2136</v>
       </c>
       <c r="J9" t="n">
-        <v>0.123</v>
+        <v>2.0424</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0824</v>
+        <v>0.7333</v>
       </c>
       <c r="L9" t="n">
-        <v>0.0406</v>
+        <v>1.3092</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.284</v>
+        <v>-0.2454</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.145</v>
+        <v>0.8502</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.139</v>
+        <v>-1.0956</v>
       </c>
       <c r="P9" t="n">
-        <v>0.3881</v>
+        <v>1.7463</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>0.3881</v>
+        <v>1.7463</v>
       </c>
       <c r="S9" t="n">
-        <v>0.5629999999999999</v>
+        <v>0.5487</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.2423</v>
+        <v>0.3805</v>
       </c>
       <c r="U9" t="n">
-        <v>0.8053</v>
+        <v>0.1683</v>
       </c>
       <c r="V9" t="n">
-        <v>0.4809</v>
+        <v>-2.9564</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>-0.3299</v>
       </c>
       <c r="X9" t="n">
-        <v>0.4809</v>
+        <v>-2.6265</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>0.8534</v>
+        <v>0.2317</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.6087</v>
+        <v>-1.1487</v>
       </c>
       <c r="F10" t="n">
-        <v>1.4621</v>
+        <v>1.3803</v>
       </c>
       <c r="G10" t="n">
         <v>-0.4452</v>
@@ -1234,13 +1234,13 @@
         <v>1.1642</v>
       </c>
       <c r="S10" t="n">
-        <v>1.2072</v>
+        <v>0.5855</v>
       </c>
       <c r="T10" t="n">
-        <v>0.6202</v>
+        <v>0.08019999999999999</v>
       </c>
       <c r="U10" t="n">
-        <v>0.5871</v>
+        <v>0.5053</v>
       </c>
       <c r="V10" t="n">
         <v>-1.0728</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.645</v>
+        <v>-0.9332</v>
       </c>
       <c r="E11" t="n">
-        <v>0.1741</v>
+        <v>-0.0051</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.819</v>
+        <v>-0.9281</v>
       </c>
       <c r="G11" t="n">
         <v>0.548</v>
@@ -1312,13 +1312,13 @@
         <v>0.9702</v>
       </c>
       <c r="S11" t="n">
-        <v>0.6429</v>
+        <v>0.3547</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.0595</v>
+        <v>-0.2386</v>
       </c>
       <c r="U11" t="n">
-        <v>0.7023</v>
+        <v>0.5933</v>
       </c>
       <c r="V11" t="n">
         <v>-1.8358</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.1613</v>
+        <v>-1.3761</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.8733</v>
+        <v>-2.2516</v>
       </c>
       <c r="F12" t="n">
-        <v>0.712</v>
+        <v>0.8754999999999999</v>
       </c>
       <c r="G12" t="n">
         <v>-3.0802</v>
@@ -1390,13 +1390,13 @@
         <v>1.5523</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.5572</v>
+        <v>0.2279</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.7020999999999999</v>
+        <v>-0.0805</v>
       </c>
       <c r="U12" t="n">
-        <v>0.1449</v>
+        <v>0.3084</v>
       </c>
       <c r="V12" t="n">
         <v>0.894</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>17.1553</v>
+        <v>18.6696</v>
       </c>
       <c r="E13" t="n">
-        <v>5.1846</v>
+        <v>6.6988</v>
       </c>
       <c r="F13" t="n">
-        <v>11.9705</v>
+        <v>11.9704</v>
       </c>
       <c r="G13" t="n">
         <v>10.9915</v>
@@ -1447,7 +1447,7 @@
         <v>8.889799999999999</v>
       </c>
       <c r="L13" t="n">
-        <v>4.9498</v>
+        <v>4.949800000000001</v>
       </c>
       <c r="M13" t="n">
         <v>-2.848</v>
@@ -1468,19 +1468,19 @@
         <v>15.5228</v>
       </c>
       <c r="S13" t="n">
-        <v>2.0636</v>
+        <v>3.5778</v>
       </c>
       <c r="T13" t="n">
-        <v>-3.0174</v>
+        <v>-1.503</v>
       </c>
       <c r="U13" t="n">
         <v>5.0809</v>
       </c>
       <c r="V13" t="n">
-        <v>-0.7506999999999996</v>
+        <v>-0.7507</v>
       </c>
       <c r="W13" t="n">
-        <v>5.034199999999999</v>
+        <v>5.0342</v>
       </c>
       <c r="X13" t="n">
         <v>-5.785</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.5512</v>
+        <v>4.148</v>
       </c>
       <c r="E14" t="n">
-        <v>3.1045</v>
+        <v>2.7041</v>
       </c>
       <c r="F14" t="n">
-        <v>1.4467</v>
+        <v>1.4438</v>
       </c>
       <c r="G14" t="n">
         <v>1.6108</v>
@@ -1546,13 +1546,13 @@
         <v>1.7463</v>
       </c>
       <c r="S14" t="n">
-        <v>0.0179</v>
+        <v>-0.3853</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.6528</v>
+        <v>-1.0532</v>
       </c>
       <c r="U14" t="n">
-        <v>0.6707</v>
+        <v>0.6679</v>
       </c>
       <c r="V14" t="n">
         <v>1.1761</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>M. DIALLO</t>
+          <t>E. CALVO SALVE</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.4656</v>
+        <v>0.8044</v>
       </c>
       <c r="E15" t="n">
-        <v>1.9498</v>
+        <v>0.7528</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.4842</v>
+        <v>0.0516</v>
       </c>
       <c r="G15" t="n">
-        <v>-2.0752</v>
+        <v>0.193</v>
       </c>
       <c r="H15" t="n">
-        <v>-1.6008</v>
+        <v>-1.1361</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.4744</v>
+        <v>1.3291</v>
       </c>
       <c r="J15" t="n">
-        <v>1.0474</v>
+        <v>0.8737</v>
       </c>
       <c r="K15" t="n">
-        <v>0.276</v>
+        <v>0.0618</v>
       </c>
       <c r="L15" t="n">
-        <v>0.7713</v>
+        <v>0.8119</v>
       </c>
       <c r="M15" t="n">
-        <v>-3.1225</v>
+        <v>-0.6808</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.8768</v>
+        <v>-1.1979</v>
       </c>
       <c r="O15" t="n">
-        <v>-1.2458</v>
+        <v>0.5172</v>
       </c>
       <c r="P15" t="n">
-        <v>-1.5523</v>
+        <v>-0.194</v>
       </c>
       <c r="Q15" t="n">
-        <v>-2.9105</v>
+        <v>-0.9702</v>
       </c>
       <c r="R15" t="n">
-        <v>1.3582</v>
+        <v>0.7761</v>
       </c>
       <c r="S15" t="n">
-        <v>0.7512</v>
+        <v>-0.1363</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.4229</v>
+        <v>-0.3746</v>
       </c>
       <c r="U15" t="n">
-        <v>1.1741</v>
+        <v>0.2384</v>
       </c>
       <c r="V15" t="n">
-        <v>3.3418</v>
+        <v>0.9418</v>
       </c>
       <c r="W15" t="n">
-        <v>4.2358</v>
+        <v>1.2239</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.894</v>
+        <v>-0.2821</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>E. CALVO SALVE</t>
+          <t>M. DIALLO</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.0497</v>
+        <v>-0.0372</v>
       </c>
       <c r="E16" t="n">
-        <v>0.3524</v>
+        <v>1.7496</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.3027</v>
+        <v>-1.7868</v>
       </c>
       <c r="G16" t="n">
-        <v>0.193</v>
+        <v>-2.0752</v>
       </c>
       <c r="H16" t="n">
-        <v>-1.1361</v>
+        <v>-1.6008</v>
       </c>
       <c r="I16" t="n">
-        <v>1.3291</v>
+        <v>-0.4744</v>
       </c>
       <c r="J16" t="n">
-        <v>0.8737</v>
+        <v>1.0474</v>
       </c>
       <c r="K16" t="n">
-        <v>0.0618</v>
+        <v>0.276</v>
       </c>
       <c r="L16" t="n">
-        <v>0.8119</v>
+        <v>0.7713</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.6808</v>
+        <v>-3.1225</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.1979</v>
+        <v>-1.8768</v>
       </c>
       <c r="O16" t="n">
-        <v>0.5172</v>
+        <v>-1.2458</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.194</v>
+        <v>-1.5523</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0.9702</v>
+        <v>-2.9105</v>
       </c>
       <c r="R16" t="n">
-        <v>0.7761</v>
+        <v>1.3582</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.891</v>
+        <v>0.2484</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.775</v>
+        <v>-0.6231</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.116</v>
+        <v>0.8715000000000001</v>
       </c>
       <c r="V16" t="n">
-        <v>0.9418</v>
+        <v>3.3418</v>
       </c>
       <c r="W16" t="n">
-        <v>1.2239</v>
+        <v>4.2358</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.2821</v>
+        <v>-0.894</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.7496</v>
+        <v>-0.0828</v>
       </c>
       <c r="E17" t="n">
-        <v>0.5546</v>
+        <v>0.6546999999999999</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.3042</v>
+        <v>-0.7375</v>
       </c>
       <c r="G17" t="n">
         <v>0.6817</v>
@@ -1780,13 +1780,13 @@
         <v>1.7463</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.8493</v>
+        <v>-1.1824</v>
       </c>
       <c r="T17" t="n">
-        <v>-1.3325</v>
+        <v>-1.2324</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.5168</v>
+        <v>0.0499</v>
       </c>
       <c r="V17" t="n">
         <v>0.6119</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>J. HOYA MARTINEZ</t>
+          <t>F. DIAZ ZARZUELA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.7586000000000001</v>
+        <v>-0.8418</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.4021</v>
+        <v>-0.0118</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.3565</v>
+        <v>-0.83</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.5467</v>
+        <v>1.6397</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.4021</v>
+        <v>1.4418</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.1446</v>
+        <v>0.1979</v>
       </c>
       <c r="J18" t="n">
-        <v>0.0824</v>
+        <v>2.248</v>
       </c>
       <c r="K18" t="n">
-        <v>0.0824</v>
+        <v>2.1668</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>0.08119999999999999</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.629</v>
+        <v>-0.6083</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.4844</v>
+        <v>-0.725</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.1446</v>
+        <v>0.1168</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.5821</v>
+        <v>-1.1642</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.9702</v>
+        <v>-1.9403</v>
       </c>
       <c r="R18" t="n">
-        <v>0.3881</v>
+        <v>0.7761</v>
       </c>
       <c r="S18" t="n">
-        <v>0.3701</v>
+        <v>-0.3278</v>
       </c>
       <c r="T18" t="n">
-        <v>0.4856</v>
+        <v>-0.5538</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.1155</v>
+        <v>0.226</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>-0.9896</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>0.2343</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-1.2239</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>D. BUTUNOI</t>
+          <t>J. HOYA MARTINEZ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,58 +1891,58 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.9003</v>
+        <v>-0.8893</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.9496</v>
+        <v>-0.8025</v>
       </c>
       <c r="F19" t="n">
-        <v>0.0493</v>
+        <v>-0.0868</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.6152</v>
+        <v>-0.5467</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.3371</v>
+        <v>-0.4021</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.2781</v>
+        <v>-0.1446</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.6467000000000001</v>
+        <v>0.0824</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.6467000000000001</v>
+        <v>0.0824</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.9685</v>
+        <v>-0.629</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.6904</v>
+        <v>-0.4844</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.2781</v>
+        <v>-0.1446</v>
       </c>
       <c r="P19" t="n">
-        <v>0.194</v>
+        <v>-0.5821</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-0.9702</v>
       </c>
       <c r="R19" t="n">
-        <v>0.194</v>
+        <v>0.3881</v>
       </c>
       <c r="S19" t="n">
-        <v>0.5209</v>
+        <v>0.2395</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.3028</v>
+        <v>0.0852</v>
       </c>
       <c r="U19" t="n">
-        <v>0.8237</v>
+        <v>0.1542</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>F. DIAZ ZARZUELA</t>
+          <t>D. BUTUNOI</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.1271</v>
+        <v>-1.0182</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.1119</v>
+        <v>-0.8495</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.0152</v>
+        <v>-0.1688</v>
       </c>
       <c r="G20" t="n">
-        <v>1.6397</v>
+        <v>-1.6152</v>
       </c>
       <c r="H20" t="n">
-        <v>1.4418</v>
+        <v>-1.3371</v>
       </c>
       <c r="I20" t="n">
-        <v>0.1979</v>
+        <v>-0.2781</v>
       </c>
       <c r="J20" t="n">
-        <v>2.248</v>
+        <v>-0.6467000000000001</v>
       </c>
       <c r="K20" t="n">
-        <v>2.1668</v>
+        <v>-0.6467000000000001</v>
       </c>
       <c r="L20" t="n">
-        <v>0.08119999999999999</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.6083</v>
+        <v>-0.9685</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.725</v>
+        <v>-0.6904</v>
       </c>
       <c r="O20" t="n">
-        <v>0.1168</v>
+        <v>-0.2781</v>
       </c>
       <c r="P20" t="n">
-        <v>-1.1642</v>
+        <v>0.194</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.9403</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>0.7761</v>
+        <v>0.194</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.613</v>
+        <v>0.4029</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.6539</v>
+        <v>-0.2027</v>
       </c>
       <c r="U20" t="n">
-        <v>0.0409</v>
+        <v>0.6057</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.9896</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
-        <v>0.2343</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.2239</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>J. BUSTOS NGUEMA</t>
+          <t>A. ALMENARA SANABRIAS</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.0095</v>
+        <v>-1.7539</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.341</v>
+        <v>-1.3819</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.6685</v>
+        <v>-0.372</v>
       </c>
       <c r="G21" t="n">
-        <v>-2.729</v>
+        <v>-0.3477</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.9656</v>
+        <v>-0.7942</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.7634</v>
+        <v>0.4466</v>
       </c>
       <c r="J21" t="n">
-        <v>-2.5063</v>
+        <v>0.6324</v>
       </c>
       <c r="K21" t="n">
-        <v>-1.2935</v>
+        <v>0.0412</v>
       </c>
       <c r="L21" t="n">
-        <v>-1.2129</v>
+        <v>0.5911999999999999</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.2227</v>
+        <v>-0.98</v>
       </c>
       <c r="N21" t="n">
-        <v>0.3279</v>
+        <v>-0.8354</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.5506</v>
+        <v>-0.1446</v>
       </c>
       <c r="P21" t="n">
-        <v>0.3881</v>
+        <v>-0.3881</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>-0.9702</v>
       </c>
       <c r="R21" t="n">
-        <v>0.3881</v>
+        <v>0.5821</v>
       </c>
       <c r="S21" t="n">
-        <v>1.8374</v>
+        <v>-0.4063</v>
       </c>
       <c r="T21" t="n">
-        <v>1.1653</v>
+        <v>-0.3844</v>
       </c>
       <c r="U21" t="n">
-        <v>0.6721</v>
+        <v>-0.0219</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.506</v>
+        <v>-0.6119</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>-0.6597</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.506</v>
+        <v>0.0478</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A. ALMENARA SANABRIAS</t>
+          <t>J. BUSTOS NGUEMA</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.0448</v>
+        <v>-2.9555</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.482</v>
+        <v>-2.0417</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.5628</v>
+        <v>-0.9137999999999999</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.3477</v>
+        <v>-2.729</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.7942</v>
+        <v>-0.9656</v>
       </c>
       <c r="I22" t="n">
-        <v>0.4466</v>
+        <v>-1.7634</v>
       </c>
       <c r="J22" t="n">
-        <v>0.6324</v>
+        <v>-2.5063</v>
       </c>
       <c r="K22" t="n">
-        <v>0.0412</v>
+        <v>-1.2935</v>
       </c>
       <c r="L22" t="n">
-        <v>0.5911999999999999</v>
+        <v>-1.2129</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.98</v>
+        <v>-0.2227</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.8354</v>
+        <v>0.3279</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.1446</v>
+        <v>-0.5506</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.3881</v>
+        <v>0.3881</v>
       </c>
       <c r="Q22" t="n">
-        <v>-0.9702</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>0.5821</v>
+        <v>0.3881</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.6972</v>
+        <v>0.8914</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.4845</v>
+        <v>0.4646</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.2126</v>
+        <v>0.4268</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.6119</v>
+        <v>-1.506</v>
       </c>
       <c r="W22" t="n">
-        <v>-0.6597</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>0.0478</v>
+        <v>-1.506</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.0008</v>
+        <v>-3.4096</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.6476</v>
+        <v>-2.2472</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.3532</v>
+        <v>-1.1624</v>
       </c>
       <c r="G23" t="n">
         <v>-2.2156</v>
@@ -2248,13 +2248,13 @@
         <v>0.194</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.1151</v>
+        <v>0.4761</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.3634</v>
+        <v>0.037</v>
       </c>
       <c r="U23" t="n">
-        <v>0.2483</v>
+        <v>0.4391</v>
       </c>
       <c r="V23" t="n">
         <v>-0.894</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-5.0701</v>
+        <v>-4.6452</v>
       </c>
       <c r="E24" t="n">
-        <v>-6.1854</v>
+        <v>-5.785</v>
       </c>
       <c r="F24" t="n">
-        <v>1.1153</v>
+        <v>1.1398</v>
       </c>
       <c r="G24" t="n">
         <v>-1.5397</v>
@@ -2326,13 +2326,13 @@
         <v>1.5523</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.5706</v>
+        <v>-0.1458</v>
       </c>
       <c r="T24" t="n">
-        <v>-1.0902</v>
+        <v>-0.6898</v>
       </c>
       <c r="U24" t="n">
-        <v>0.5195</v>
+        <v>0.544</v>
       </c>
       <c r="V24" t="n">
         <v>-1.6015</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-5.5609</v>
+        <v>-5.0939</v>
       </c>
       <c r="E25" t="n">
-        <v>-4.8122</v>
+        <v>-4.7121</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.7487</v>
+        <v>-0.3818</v>
       </c>
       <c r="G25" t="n">
         <v>-4.0478</v>
@@ -2404,13 +2404,13 @@
         <v>0.9702</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.825</v>
+        <v>-0.3581</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.6539</v>
+        <v>-0.5538</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.1711</v>
+        <v>0.1957</v>
       </c>
       <c r="V25" t="n">
         <v>0.2821</v>
@@ -2437,13 +2437,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-17.1552</v>
+        <v>-15.775</v>
       </c>
       <c r="E26" t="n">
         <v>-11.9705</v>
       </c>
       <c r="F26" t="n">
-        <v>-5.1847</v>
+        <v>-3.8047</v>
       </c>
       <c r="G26" t="n">
         <v>-10.9917</v>
@@ -2452,13 +2452,13 @@
         <v>-10.2406</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.7509000000000012</v>
+        <v>-0.7509000000000003</v>
       </c>
       <c r="J26" t="n">
-        <v>2.848</v>
+        <v>2.848000000000002</v>
       </c>
       <c r="K26" t="n">
-        <v>-1.351</v>
+        <v>-1.351000000000001</v>
       </c>
       <c r="L26" t="n">
         <v>4.199</v>
@@ -2482,13 +2482,13 @@
         <v>10.6718</v>
       </c>
       <c r="S26" t="n">
-        <v>-2.0637</v>
+        <v>-0.6836999999999999</v>
       </c>
       <c r="T26" t="n">
         <v>-5.081</v>
       </c>
       <c r="U26" t="n">
-        <v>3.017299999999999</v>
+        <v>4.3973</v>
       </c>
       <c r="V26" t="n">
         <v>0.7507000000000001</v>
@@ -2497,7 +2497,7 @@
         <v>5.785</v>
       </c>
       <c r="X26" t="n">
-        <v>-5.034299999999999</v>
+        <v>-5.0343</v>
       </c>
     </row>
   </sheetData>
